--- a/data/tecnologia_medica/misiones.xlsx
+++ b/data/tecnologia_medica/misiones.xlsx
@@ -12,9 +12,9 @@
     <sheet name="Plan" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Misiones'!$A$1:$H$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Matriz'!$A$1:$B$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Plan'!$A$1:$H$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Misiones'!$A$1:$H$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Matriz'!$A$1:$D$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Plan'!$A$1:$H$56</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -468,16 +468,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="51" customWidth="1" min="7" max="7"/>
+    <col width="55" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -537,22 +537,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>revision_guia</t>
+          <t>construir_control</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>p6, p1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Revisión de guía y pauta.</t>
+          <t>Construcción del control. — Control lógica 2, 15 min</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -563,11 +563,11 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
+        <v>46102</v>
+      </c>
+      <c r="B3" s="3" t="n">
         <v>46107</v>
       </c>
-      <c r="B3" s="3" t="n">
-        <v>46114</v>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>Control</t>
@@ -575,22 +575,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>revision_guia</t>
+          <t>pauta_prueba</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p2, p5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Revisión de guía y pauta.</t>
+          <t>Pauta del control. — Control lógica 2, 15 min</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -601,34 +601,34 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46121</v>
+        <v>46107</v>
       </c>
       <c r="B4" s="3" t="n">
-        <v>46128</v>
+        <v>46114</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Certamen</t>
+          <t>Control</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>revision_guia</t>
+          <t>construir_control</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p2, p3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Revisión de guía y pauta.</t>
+          <t>Construcción del control. — Control lógica 3, 15 min</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -639,10 +639,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46135</v>
+        <v>46109</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>46142</v>
+        <v>46107</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -651,22 +651,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>revision_guia</t>
+          <t>escanear</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Revisión de guía y pauta.</t>
+          <t>Escanear control y subir a carpeta. — Control lógica 2, 15 min</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -677,10 +677,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46142</v>
+        <v>46109</v>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46149</v>
+        <v>46114</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -689,22 +689,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>revision_guia</t>
+          <t>pauta_prueba</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p1, p6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Revisión de guía y pauta.</t>
+          <t>Pauta del control. — Control lógica 3, 15 min</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -715,34 +715,34 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46149</v>
+        <v>46114</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>46156</v>
+        <v>46128</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Certamen</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>revision_guia</t>
+          <t>pedir_preguntas</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>Todos</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Revisión de guía y pauta.</t>
+          <t>Cada profesor propone preguntas para el certamen. — Certamen 1</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -753,34 +753,34 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46163</v>
+        <v>46116</v>
       </c>
       <c r="B8" s="3" t="n">
-        <v>46170</v>
+        <v>46114</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Certamen</t>
+          <t>Control</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>revision_guia</t>
+          <t>escanear</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Revisión de guía y pauta.</t>
+          <t>Escanear control y subir a carpeta. — Control lógica 3, 15 min</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -791,34 +791,34 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46184</v>
+        <v>46121</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>46191</v>
+        <v>46128</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Certamen</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>revision_guia</t>
+          <t>construir_control</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>p1, p2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Revisión de guía y pauta.</t>
+          <t>Construcción del certamen. — Certamen 1</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -829,10 +829,10 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46191</v>
+        <v>46121</v>
       </c>
       <c r="B10" s="3" t="n">
-        <v>46198</v>
+        <v>46107</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -841,22 +841,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>revision_guia</t>
+          <t>corregir_y_notas</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Revisión de guía y pauta.</t>
+          <t>Corregir control y subir notas. — Control lógica 2, 15 min</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -867,34 +867,34 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46191</v>
+        <v>46123</v>
       </c>
       <c r="B11" s="3" t="n">
-        <v>46177</v>
+        <v>46128</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Trabajo práctico</t>
+          <t>Certamen</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>revisar_tp</t>
+          <t>pauta_prueba</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Todos</t>
+          <t>p3, p4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Revisar TP y poner nota; subir rúbrica si aplica.</t>
+          <t>Pauta del certamen. — Certamen 1</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -905,10 +905,10 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>46198</v>
+        <v>46125</v>
       </c>
       <c r="B12" s="3" t="n">
-        <v>46205</v>
+        <v>46128</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -917,22 +917,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>revision_guia</t>
+          <t>revisar_prueba</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>p5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Revisión de guía y pauta.</t>
+          <t>Revisión final del certamen. — Certamen 1</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -943,34 +943,34 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46198</v>
+        <v>46128</v>
       </c>
       <c r="B13" s="3" t="n">
-        <v>46219</v>
+        <v>46114</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Examen</t>
+          <t>Control</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>pedir_preguntas</t>
+          <t>corregir_y_notas</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Todos</t>
+          <t>p5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Preguntas para examen (temas por unidad).</t>
+          <t>Corregir control y subir notas. — Control lógica 3, 15 min</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -981,34 +981,34 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>46205</v>
+        <v>46130</v>
       </c>
       <c r="B14" s="3" t="n">
-        <v>46219</v>
+        <v>46128</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Examen</t>
+          <t>Certamen</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>construir_examen</t>
+          <t>escanear</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>p4, p5</t>
+          <t>p6</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Construcción examen final + revisión cruzada.</t>
+          <t>Escanear certamen y subir a carpeta. — Certamen 1</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1019,34 +1019,34 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>46205</v>
+        <v>46135</v>
       </c>
       <c r="B15" s="3" t="n">
-        <v>46226</v>
+        <v>46142</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Examen</t>
+          <t>Control</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>pedir_preguntas</t>
+          <t>construir_control</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Todos</t>
+          <t>p2, p6</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Preguntas para examen (temas por unidad).</t>
+          <t>Construcción del control. — Control Modelos y Derivadas 2, 15 min</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1057,34 +1057,34 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>46212</v>
+        <v>46137</v>
       </c>
       <c r="B16" s="3" t="n">
-        <v>46219</v>
+        <v>46142</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Examen</t>
+          <t>Control</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>pauta_examen</t>
+          <t>pauta_prueba</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>p1, p2</t>
+          <t>p1, p4</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pauta oficial examen.</t>
+          <t>Pauta del control. — Control Modelos y Derivadas 2, 15 min</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1095,34 +1095,34 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>46212</v>
+        <v>46142</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>46226</v>
+        <v>46128</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Examen</t>
+          <t>Certamen</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>construir_examen</t>
+          <t>corregir_y_notas</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>p4, p5</t>
+          <t>p5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Construcción examen final + revisión cruzada.</t>
+          <t>Corregir certamen y subir notas. — Certamen 1</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1133,34 +1133,34 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>46219</v>
+        <v>46142</v>
       </c>
       <c r="B18" s="3" t="n">
-        <v>46226</v>
+        <v>46149</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Examen</t>
+          <t>Control</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>pauta_examen</t>
+          <t>construir_control</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>p6, p5</t>
+          <t>p3, p6</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pauta oficial examen.</t>
+          <t>Construcción del control. — Control Modelos y Derivadas 3, 15 min</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1171,24 +1171,24 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>46233</v>
+        <v>46144</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>46219</v>
+        <v>46142</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Examen</t>
+          <t>Control</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>corregir_examen</t>
+          <t>escanear</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Corrección examen por sección.</t>
+          <t>Escanear control y subir a carpeta. — Control Modelos y Derivadas 2, 15 min</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1209,44 +1209,1412 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>46149</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>pauta_prueba</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>p4, p5</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Pauta del control. — Control Modelos y Derivadas 3, 15 min</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>46156</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>construir_control</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>p4, p1</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Construcción del control. — Control Modelos y Derivadas 4, 15 min</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>46149</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>escanear</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Escanear control y subir a carpeta. — Control Modelos y Derivadas 3, 15 min</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>46156</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>pauta_prueba</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>p3, p6</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Pauta del control. — Control Modelos y Derivadas 4, 15 min</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>46170</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Certamen</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>pedir_preguntas</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Cada profesor propone preguntas para el certamen. — Certamen 2</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>46142</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>corregir_y_notas</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Corregir control y subir notas. — Control Modelos y Derivadas 2, 15 min</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>46156</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>escanear</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>p5</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Escanear control y subir a carpeta. — Control Modelos y Derivadas 4, 15 min</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>46170</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Certamen</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>construir_control</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>p4, p5</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Construcción del certamen. — Certamen 2</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>46149</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>corregir_y_notas</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Corregir control y subir notas. — Control Modelos y Derivadas 3, 15 min</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>46170</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Certamen</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>pauta_prueba</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>p1, p6</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Pauta del certamen. — Certamen 2</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>46167</v>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>46170</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Certamen</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>revisar_prueba</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Revisión final del certamen. — Certamen 2</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>46156</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>corregir_y_notas</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>p3</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Corregir control y subir notas. — Control Modelos y Derivadas 4, 15 min</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>46172</v>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>46170</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Certamen</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>escanear</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>p4</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Escanear certamen y subir a carpeta. — Certamen 2</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>46170</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Certamen</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>corregir_y_notas</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Corregir certamen y subir notas. — Certamen 2</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>46191</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>construir_control</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>p5, p6</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Construcción del control. — Control Trigonometría y Vectores 2, 15 min</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>46191</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>pauta_prueba</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>p3, p2</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Pauta del control. — Control Trigonometría y Vectores 2, 15 min</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>46191</v>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>46205</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Certamen</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>pedir_preguntas</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Cada profesor propone preguntas para el certamen. — Certamen 3</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>46191</v>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>46198</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>construir_control</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>p2, p5</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Construcción del control. — Control Trigonometría y Vectores 3, 15 min</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>46191</v>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>46177</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Trabajo práctico</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>revisar_tp</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Revisar TP y subir nota. — Trabajo Práctico</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>46193</v>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>46191</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>escanear</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>p6</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Escanear control y subir a carpeta. — Control Trigonometría y Vectores 2, 15 min</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>46193</v>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>46198</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>pauta_prueba</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>p3, p4</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Pauta del control. — Control Trigonometría y Vectores 3, 15 min</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>46198</v>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>46205</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Certamen</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>construir_control</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>p2, p5</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Construcción del certamen. — Certamen 3</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>46198</v>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>46219</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>pedir_preguntas</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Preguntas para examen. — Virgen del Carmen</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>46200</v>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>46205</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Certamen</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>pauta_prueba</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>p6, p4</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Pauta del certamen. — Certamen 3</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>46200</v>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>46198</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>escanear</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Escanear control y subir a carpeta. — Control Trigonometría y Vectores 3, 15 min</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>46205</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Certamen</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>revisar_prueba</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>p6</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Revisión final del certamen. — Certamen 3</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>46191</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>corregir_y_notas</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Corregir control y subir notas. — Control Trigonometría y Vectores 2, 15 min</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>46219</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>construir_examen</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>p4, p5</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Construcción del examen. — Virgen del Carmen</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>46226</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>pedir_preguntas</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Preguntas para examen. — Examen 2</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>46207</v>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>46205</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Certamen</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>escanear</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>p3</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Escanear certamen y subir a carpeta. — Certamen 3</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>46198</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>corregir_y_notas</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>p3</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Corregir control y subir notas. — Control Trigonometría y Vectores 3, 15 min</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>46219</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>pauta_examen</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>p1, p4</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Pauta del examen. — Virgen del Carmen</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>46226</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>construir_examen</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>p3, p6</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Construcción del examen. — Examen 2</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>46205</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Certamen</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>corregir_y_notas</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Corregir certamen y subir notas. — Certamen 3</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>46226</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>pauta_examen</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>p2, p5</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Pauta del examen. — Examen 2</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>46219</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>corregir_examen</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Corregir examen. — Virgen del Carmen</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
         <v>46240</v>
       </c>
-      <c r="B20" s="3" t="n">
+      <c r="B56" s="3" t="n">
         <v>46226</v>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>Examen</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>corregir_examen</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Sección 1</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Corrección examen por sección.</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>p4</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Corregir examen. — Examen 2</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H20"/>
+  <autoFilter ref="A1:H56"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1257,51 +2625,1249 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:D56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Evaluaciones</t>
+          <t>Evaluación</t>
         </is>
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>Sección 1 (lunes - DA)</t>
+          <t>Misión</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Detalle</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Sección 2 (Jueves)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Examen</t>
+          <t>Certamen</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>construir_control</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Construcción del certamen. — Certamen 1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>p1, p2</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>Certamen</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>construir_control</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Construcción del certamen. — Certamen 2</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>p4, p5</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Certamen</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>construir_control</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Construcción del certamen. — Certamen 3</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>p2, p5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Certamen</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>corregir_y_notas</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Corregir certamen y subir notas. — Certamen 1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>p5</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Certamen</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>corregir_y_notas</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Corregir certamen y subir notas. — Certamen 2</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>p1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Certamen</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>corregir_y_notas</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Corregir certamen y subir notas. — Certamen 3</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>p2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Certamen</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>escanear</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Escanear certamen y subir a carpeta. — Certamen 1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>p6</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Certamen</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>escanear</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Escanear certamen y subir a carpeta. — Certamen 2</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>p4</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Certamen</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>escanear</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Escanear certamen y subir a carpeta. — Certamen 3</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>p3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Certamen</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>pauta_prueba</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Pauta del certamen. — Certamen 1</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>p3, p4</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Certamen</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>pauta_prueba</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Pauta del certamen. — Certamen 2</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>p1, p6</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Certamen</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>pauta_prueba</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Pauta del certamen. — Certamen 3</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>p6, p4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Certamen</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>pedir_preguntas</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Cada profesor propone preguntas para el certamen. — Certamen 1</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Certamen</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>pedir_preguntas</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Cada profesor propone preguntas para el certamen. — Certamen 2</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Certamen</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>pedir_preguntas</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Cada profesor propone preguntas para el certamen. — Certamen 3</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Certamen</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>revisar_prueba</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Revisión final del certamen. — Certamen 1</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>p5</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Certamen</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>revisar_prueba</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Revisión final del certamen. — Certamen 2</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>p2</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Certamen</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>revisar_prueba</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Revisión final del certamen. — Certamen 3</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>p6</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>construir_control</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Construcción del control. — Control Modelos y Derivadas 2, 15 min</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>p2, p6</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>construir_control</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Construcción del control. — Control Modelos y Derivadas 3, 15 min</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>p3, p6</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>construir_control</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Construcción del control. — Control Modelos y Derivadas 4, 15 min</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>p4, p1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>construir_control</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Construcción del control. — Control Trigonometría y Vectores 2, 15 min</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>p5, p6</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>construir_control</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Construcción del control. — Control Trigonometría y Vectores 3, 15 min</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>p2, p5</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>construir_control</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Construcción del control. — Control lógica 2, 15 min</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>p6, p1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>construir_control</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Construcción del control. — Control lógica 3, 15 min</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>p2, p3</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>corregir_y_notas</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Corregir control y subir notas. — Control Modelos y Derivadas 2, 15 min</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>p1</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>corregir_y_notas</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Corregir control y subir notas. — Control Modelos y Derivadas 3, 15 min</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>p2</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>corregir_y_notas</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Corregir control y subir notas. — Control Modelos y Derivadas 4, 15 min</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>p3</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>corregir_y_notas</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Corregir control y subir notas. — Control Trigonometría y Vectores 2, 15 min</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>p1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>corregir_y_notas</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Corregir control y subir notas. — Control Trigonometría y Vectores 3, 15 min</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>p3</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>corregir_y_notas</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Corregir control y subir notas. — Control lógica 2, 15 min</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>p3</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>corregir_y_notas</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Corregir control y subir notas. — Control lógica 3, 15 min</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>p5</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>escanear</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Escanear control y subir a carpeta. — Control Modelos y Derivadas 2, 15 min</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>p3</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>escanear</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Escanear control y subir a carpeta. — Control Modelos y Derivadas 3, 15 min</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>p2</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>escanear</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Escanear control y subir a carpeta. — Control Modelos y Derivadas 4, 15 min</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>p5</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>escanear</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Escanear control y subir a carpeta. — Control Trigonometría y Vectores 2, 15 min</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>p6</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>escanear</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Escanear control y subir a carpeta. — Control Trigonometría y Vectores 3, 15 min</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>p1</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>escanear</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Escanear control y subir a carpeta. — Control lógica 2, 15 min</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>p4</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>escanear</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Escanear control y subir a carpeta. — Control lógica 3, 15 min</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>p4</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>pauta_prueba</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Pauta del control. — Control Modelos y Derivadas 2, 15 min</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>p1, p4</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>pauta_prueba</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Pauta del control. — Control Modelos y Derivadas 3, 15 min</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>p4, p5</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>pauta_prueba</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Pauta del control. — Control Modelos y Derivadas 4, 15 min</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>p3, p6</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>pauta_prueba</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Pauta del control. — Control Trigonometría y Vectores 2, 15 min</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>p3, p2</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>pauta_prueba</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Pauta del control. — Control Trigonometría y Vectores 3, 15 min</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>p3, p4</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>pauta_prueba</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Pauta del control. — Control lógica 2, 15 min</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>p2, p5</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>pauta_prueba</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Pauta del control. — Control lógica 3, 15 min</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>p1, p6</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>construir_examen</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Construcción del examen. — Examen 2</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>p3, p6</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>construir_examen</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Construcción del examen. — Virgen del Carmen</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>p4, p5</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>corregir_examen</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Corregir examen. — Examen 2</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>p4</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>corregir_examen</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Corregir examen. — Virgen del Carmen</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>p1</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>pauta_examen</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Pauta del examen. — Examen 2</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>p2, p5</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>pauta_examen</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Pauta del examen. — Virgen del Carmen</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>p1, p4</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>pedir_preguntas</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Preguntas para examen. — Examen 2</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>pedir_preguntas</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Preguntas para examen. — Virgen del Carmen</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>Trabajo práctico</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>revisar_tp</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Revisar TP y subir nota. — Trabajo Práctico</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B3"/>
+  <autoFilter ref="A1:D56"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1312,16 +3878,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="51" customWidth="1" min="7" max="7"/>
+    <col width="55" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -1369,7 +3935,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>46121</v>
+        <v>46114</v>
       </c>
       <c r="B2" s="3" t="n">
         <v>46128</v>
@@ -1381,22 +3947,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>revision_guia</t>
+          <t>pedir_preguntas</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>Todos</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Revisión de guía y pauta.</t>
+          <t>Cada profesor propone preguntas para el certamen. — Certamen 1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1407,7 +3973,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>46163</v>
+        <v>46156</v>
       </c>
       <c r="B3" s="3" t="n">
         <v>46170</v>
@@ -1419,22 +3985,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>revision_guia</t>
+          <t>pedir_preguntas</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>Todos</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Revisión de guía y pauta.</t>
+          <t>Cada profesor propone preguntas para el certamen. — Certamen 2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1445,7 +4011,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>46198</v>
+        <v>46191</v>
       </c>
       <c r="B4" s="3" t="n">
         <v>46205</v>
@@ -1457,22 +4023,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>revision_guia</t>
+          <t>pedir_preguntas</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>Todos</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Revisión de guía y pauta.</t>
+          <t>Cada profesor propone preguntas para el certamen. — Certamen 3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1483,34 +4049,34 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>46100</v>
+        <v>46121</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>46107</v>
+        <v>46128</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Certamen</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>revision_guia</t>
+          <t>construir_control</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>p1, p2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Revisión de guía y pauta.</t>
+          <t>Construcción del certamen. — Certamen 1</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1521,34 +4087,34 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>46107</v>
+        <v>46163</v>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46114</v>
+        <v>46170</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Certamen</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>revision_guia</t>
+          <t>construir_control</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p4, p5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Revisión de guía y pauta.</t>
+          <t>Construcción del certamen. — Certamen 2</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1559,34 +4125,34 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>46135</v>
+        <v>46198</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>46142</v>
+        <v>46205</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Certamen</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>revision_guia</t>
+          <t>construir_control</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p2, p5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Revisión de guía y pauta.</t>
+          <t>Construcción del certamen. — Certamen 3</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1597,34 +4163,34 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>46142</v>
+        <v>46123</v>
       </c>
       <c r="B8" s="3" t="n">
-        <v>46149</v>
+        <v>46128</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Certamen</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>revision_guia</t>
+          <t>pauta_prueba</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p3, p4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Revisión de guía y pauta.</t>
+          <t>Pauta del certamen. — Certamen 1</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1635,34 +4201,34 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>46149</v>
+        <v>46165</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>46156</v>
+        <v>46170</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Certamen</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>revision_guia</t>
+          <t>pauta_prueba</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>p1, p6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Revisión de guía y pauta.</t>
+          <t>Pauta del certamen. — Certamen 2</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1673,34 +4239,34 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>46184</v>
+        <v>46200</v>
       </c>
       <c r="B10" s="3" t="n">
-        <v>46191</v>
+        <v>46205</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Certamen</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>revision_guia</t>
+          <t>pauta_prueba</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>p6, p4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Revisión de guía y pauta.</t>
+          <t>Pauta del certamen. — Certamen 3</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1711,34 +4277,34 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>46191</v>
+        <v>46125</v>
       </c>
       <c r="B11" s="3" t="n">
-        <v>46198</v>
+        <v>46128</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Certamen</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>revision_guia</t>
+          <t>revisar_prueba</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Revisión de guía y pauta.</t>
+          <t>Revisión final del certamen. — Certamen 1</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1749,34 +4315,34 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>46198</v>
+        <v>46167</v>
       </c>
       <c r="B12" s="3" t="n">
-        <v>46219</v>
+        <v>46170</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Examen</t>
+          <t>Certamen</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>pedir_preguntas</t>
+          <t>revisar_prueba</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Todos</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Preguntas para examen (temas por unidad).</t>
+          <t>Revisión final del certamen. — Certamen 2</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1787,34 +4353,34 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B13" s="3" t="n">
         <v>46205</v>
       </c>
-      <c r="B13" s="3" t="n">
-        <v>46226</v>
-      </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Examen</t>
+          <t>Certamen</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>pedir_preguntas</t>
+          <t>revisar_prueba</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Todos</t>
+          <t>p6</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Preguntas para examen (temas por unidad).</t>
+          <t>Revisión final del certamen. — Certamen 3</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1825,34 +4391,34 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>46205</v>
+        <v>46130</v>
       </c>
       <c r="B14" s="3" t="n">
-        <v>46219</v>
+        <v>46128</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Examen</t>
+          <t>Certamen</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>construir_examen</t>
+          <t>escanear</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>p4, p5</t>
+          <t>p6</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Construcción examen final + revisión cruzada.</t>
+          <t>Escanear certamen y subir a carpeta. — Certamen 1</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1863,34 +4429,34 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>46212</v>
+        <v>46172</v>
       </c>
       <c r="B15" s="3" t="n">
-        <v>46226</v>
+        <v>46170</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Examen</t>
+          <t>Certamen</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>construir_examen</t>
+          <t>escanear</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>p4, p5</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Construcción examen final + revisión cruzada.</t>
+          <t>Escanear certamen y subir a carpeta. — Certamen 2</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1901,34 +4467,34 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>46212</v>
+        <v>46207</v>
       </c>
       <c r="B16" s="3" t="n">
-        <v>46219</v>
+        <v>46205</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Examen</t>
+          <t>Certamen</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>pauta_examen</t>
+          <t>escanear</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>p1, p2</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pauta oficial examen.</t>
+          <t>Escanear certamen y subir a carpeta. — Certamen 3</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1939,34 +4505,34 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>46219</v>
+        <v>46142</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>46226</v>
+        <v>46128</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Examen</t>
+          <t>Certamen</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>pauta_examen</t>
+          <t>corregir_y_notas</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>p6, p5</t>
+          <t>p5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pauta oficial examen.</t>
+          <t>Corregir certamen y subir notas. — Certamen 1</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1977,34 +4543,34 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>46233</v>
+        <v>46184</v>
       </c>
       <c r="B18" s="3" t="n">
-        <v>46219</v>
+        <v>46170</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Examen</t>
+          <t>Certamen</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>corregir_examen</t>
+          <t>corregir_y_notas</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Corrección examen por sección.</t>
+          <t>Corregir certamen y subir notas. — Certamen 2</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2015,24 +4581,24 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>46240</v>
+        <v>46219</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>46226</v>
+        <v>46205</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Examen</t>
+          <t>Certamen</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>corregir_examen</t>
+          <t>corregir_y_notas</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2042,7 +4608,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Corrección examen por sección.</t>
+          <t>Corregir certamen y subir notas. — Certamen 3</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2053,44 +4619,1412 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>46107</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>construir_control</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>p6, p1</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Construcción del control. — Control lógica 2, 15 min</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>46114</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>construir_control</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>p2, p3</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Construcción del control. — Control lógica 3, 15 min</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>46142</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>construir_control</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>p2, p6</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Construcción del control. — Control Modelos y Derivadas 2, 15 min</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>46149</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>construir_control</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>p3, p6</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Construcción del control. — Control Modelos y Derivadas 3, 15 min</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>46156</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>construir_control</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>p4, p1</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Construcción del control. — Control Modelos y Derivadas 4, 15 min</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B25" s="3" t="n">
         <v>46191</v>
       </c>
-      <c r="B20" s="3" t="n">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>construir_control</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>p5, p6</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Construcción del control. — Control Trigonometría y Vectores 2, 15 min</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="n">
+        <v>46191</v>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>46198</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>construir_control</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>p2, p5</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Construcción del control. — Control Trigonometría y Vectores 3, 15 min</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>46102</v>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>46107</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>pauta_prueba</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>p2, p5</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Pauta del control. — Control lógica 2, 15 min</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="n">
+        <v>46109</v>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>46114</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>pauta_prueba</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>p1, p6</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Pauta del control. — Control lógica 3, 15 min</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>46137</v>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>46142</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>pauta_prueba</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>p1, p4</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Pauta del control. — Control Modelos y Derivadas 2, 15 min</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>46149</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>pauta_prueba</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>p4, p5</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Pauta del control. — Control Modelos y Derivadas 3, 15 min</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>46156</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>pauta_prueba</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>p3, p6</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Pauta del control. — Control Modelos y Derivadas 4, 15 min</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>46191</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>pauta_prueba</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>p3, p2</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Pauta del control. — Control Trigonometría y Vectores 2, 15 min</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>46193</v>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>46198</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>pauta_prueba</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>p3, p4</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Pauta del control. — Control Trigonometría y Vectores 3, 15 min</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="n">
+        <v>46109</v>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>46107</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>escanear</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>p4</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Escanear control y subir a carpeta. — Control lógica 2, 15 min</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>46116</v>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>46114</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>escanear</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>p4</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Escanear control y subir a carpeta. — Control lógica 3, 15 min</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>46142</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>escanear</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>p3</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Escanear control y subir a carpeta. — Control Modelos y Derivadas 2, 15 min</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>46149</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>escanear</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Escanear control y subir a carpeta. — Control Modelos y Derivadas 3, 15 min</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>46156</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>escanear</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>p5</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Escanear control y subir a carpeta. — Control Modelos y Derivadas 4, 15 min</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="n">
+        <v>46193</v>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>46191</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>escanear</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>p6</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Escanear control y subir a carpeta. — Control Trigonometría y Vectores 2, 15 min</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="n">
+        <v>46200</v>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>46198</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>escanear</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Escanear control y subir a carpeta. — Control Trigonometría y Vectores 3, 15 min</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="n">
+        <v>46121</v>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>46107</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>corregir_y_notas</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>p3</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Corregir control y subir notas. — Control lógica 2, 15 min</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="n">
+        <v>46128</v>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>46114</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>corregir_y_notas</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>p5</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Corregir control y subir notas. — Control lógica 3, 15 min</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>46142</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>corregir_y_notas</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Corregir control y subir notas. — Control Modelos y Derivadas 2, 15 min</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>46149</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>corregir_y_notas</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Corregir control y subir notas. — Control Modelos y Derivadas 3, 15 min</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>46156</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>corregir_y_notas</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>p3</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Corregir control y subir notas. — Control Modelos y Derivadas 4, 15 min</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>46191</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>corregir_y_notas</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Corregir control y subir notas. — Control Trigonometría y Vectores 2, 15 min</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>46198</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>corregir_y_notas</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>p3</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Corregir control y subir notas. — Control Trigonometría y Vectores 3, 15 min</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="n">
+        <v>46198</v>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>46219</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>pedir_preguntas</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Preguntas para examen. — Virgen del Carmen</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>46226</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>pedir_preguntas</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Preguntas para examen. — Examen 2</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>46219</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>construir_examen</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>p4, p5</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Construcción del examen. — Virgen del Carmen</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>46226</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>construir_examen</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>p3, p6</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Construcción del examen. — Examen 2</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>46219</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>pauta_examen</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>p1, p4</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Pauta del examen. — Virgen del Carmen</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>46226</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>pauta_examen</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>p2, p5</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Pauta del examen. — Examen 2</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>46219</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>corregir_examen</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Corregir examen. — Virgen del Carmen</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>46226</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>corregir_examen</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>p4</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Corregir examen. — Examen 2</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="n">
+        <v>46191</v>
+      </c>
+      <c r="B56" s="3" t="n">
         <v>46177</v>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>Trabajo práctico</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>revisar_tp</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Sección 1</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Revisar TP y poner nota; subir rúbrica si aplica.</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Revisar TP y subir nota. — Trabajo Práctico</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H20"/>
+  <autoFilter ref="A1:H56"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/tecnologia_medica/misiones.xlsx
+++ b/data/tecnologia_medica/misiones.xlsx
@@ -547,7 +547,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>p6, p1</t>
+          <t>p1, p2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>p2, p5</t>
+          <t>p4, p3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>p2, p3</t>
+          <t>p3, p4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -661,7 +661,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>p1, p6</t>
+          <t>p4, p1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>p1, p2</t>
+          <t>p2, p1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -965,7 +965,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>p2, p6</t>
+          <t>p2, p1</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>p1, p4</t>
+          <t>p2, p4</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>p3, p6</t>
+          <t>p1, p2</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>p4, p5</t>
+          <t>p4, p1</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>p4, p1</t>
+          <t>p3, p2</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>p3, p6</t>
+          <t>p3, p4</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>p4, p5</t>
+          <t>p3, p1</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>p1, p6</t>
+          <t>p2, p1</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>p5, p6</t>
+          <t>p2, p4</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>p3, p2</t>
+          <t>p1, p3</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>p2, p5</t>
+          <t>p1, p4</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>p3, p4</t>
+          <t>p1, p3</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>p2, p5</t>
+          <t>p3, p1</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>p6, p4</t>
+          <t>p4, p2</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>p4, p5</t>
+          <t>p1, p4</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>p1, p4</t>
+          <t>p3, p1</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>p3, p6</t>
+          <t>p2, p3</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>p2, p5</t>
+          <t>p4, p1</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>p1, p2</t>
+          <t>p2, p1</t>
         </is>
       </c>
     </row>
@@ -2696,7 +2696,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>p4, p5</t>
+          <t>p3, p1</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>p2, p5</t>
+          <t>p3, p1</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p3</t>
         </is>
       </c>
     </row>
@@ -2762,7 +2762,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p2</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p3</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>p1</t>
         </is>
       </c>
     </row>
@@ -2828,7 +2828,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p3</t>
         </is>
       </c>
     </row>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>p4</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>p1, p6</t>
+          <t>p2, p1</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>p6, p4</t>
+          <t>p4, p2</t>
         </is>
       </c>
     </row>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p4</t>
         </is>
       </c>
     </row>
@@ -3026,7 +3026,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p4</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>p2</t>
         </is>
       </c>
     </row>
@@ -3070,7 +3070,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>p2, p6</t>
+          <t>p2, p1</t>
         </is>
       </c>
     </row>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>p3, p6</t>
+          <t>p1, p2</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>p4, p1</t>
+          <t>p3, p2</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>p5, p6</t>
+          <t>p2, p4</t>
         </is>
       </c>
     </row>
@@ -3158,7 +3158,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>p2, p5</t>
+          <t>p1, p4</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>p6, p1</t>
+          <t>p1, p2</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>p2, p3</t>
+          <t>p3, p4</t>
         </is>
       </c>
     </row>
@@ -3224,7 +3224,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p3</t>
         </is>
       </c>
     </row>
@@ -3246,7 +3246,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p4</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>p4</t>
         </is>
       </c>
     </row>
@@ -3290,7 +3290,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p3</t>
         </is>
       </c>
     </row>
@@ -3312,7 +3312,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>p2</t>
         </is>
       </c>
     </row>
@@ -3334,7 +3334,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>p1</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p3</t>
         </is>
       </c>
     </row>
@@ -3422,7 +3422,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p1</t>
         </is>
       </c>
     </row>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>p2</t>
         </is>
       </c>
     </row>
@@ -3466,7 +3466,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p4</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p2</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p2</t>
         </is>
       </c>
     </row>
@@ -3532,7 +3532,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>p1, p4</t>
+          <t>p2, p4</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3554,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>p4, p5</t>
+          <t>p4, p1</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>p3, p6</t>
+          <t>p3, p4</t>
         </is>
       </c>
     </row>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>p3, p2</t>
+          <t>p1, p3</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>p3, p4</t>
+          <t>p1, p3</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>p2, p5</t>
+          <t>p4, p3</t>
         </is>
       </c>
     </row>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>p1, p6</t>
+          <t>p4, p1</t>
         </is>
       </c>
     </row>
@@ -3686,7 +3686,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>p3, p6</t>
+          <t>p2, p3</t>
         </is>
       </c>
     </row>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>p4, p5</t>
+          <t>p1, p4</t>
         </is>
       </c>
     </row>
@@ -3730,7 +3730,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p2</t>
         </is>
       </c>
     </row>
@@ -3752,7 +3752,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p2</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>p2, p5</t>
+          <t>p4, p1</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>p1, p4</t>
+          <t>p3, p1</t>
         </is>
       </c>
     </row>
@@ -4071,7 +4071,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>p1, p2</t>
+          <t>p2, p1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>p4, p5</t>
+          <t>p3, p1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>p2, p5</t>
+          <t>p3, p1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>p1, p6</t>
+          <t>p2, p1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>p6, p4</t>
+          <t>p4, p2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -4375,7 +4375,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -4565,7 +4565,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4603,7 +4603,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>p6, p1</t>
+          <t>p1, p2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>p2, p3</t>
+          <t>p3, p4</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -4717,7 +4717,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>p2, p6</t>
+          <t>p2, p1</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>p3, p6</t>
+          <t>p1, p2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -4793,7 +4793,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>p4, p1</t>
+          <t>p3, p2</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>p5, p6</t>
+          <t>p2, p4</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>p2, p5</t>
+          <t>p1, p4</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>p2, p5</t>
+          <t>p4, p3</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>p1, p6</t>
+          <t>p4, p1</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4983,7 +4983,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>p1, p4</t>
+          <t>p2, p4</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -5021,7 +5021,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>p4, p5</t>
+          <t>p4, p1</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -5059,7 +5059,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>p3, p6</t>
+          <t>p3, p4</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>p3, p2</t>
+          <t>p1, p3</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>p3, p4</t>
+          <t>p1, p3</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5325,7 +5325,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5439,7 +5439,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -5515,7 +5515,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -5667,7 +5667,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>p4, p5</t>
+          <t>p1, p4</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>p3, p6</t>
+          <t>p2, p3</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5857,7 +5857,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>p1, p4</t>
+          <t>p3, p1</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5895,7 +5895,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>p2, p5</t>
+          <t>p4, p1</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">

--- a/data/tecnologia_medica/misiones.xlsx
+++ b/data/tecnologia_medica/misiones.xlsx
@@ -9,12 +9,16 @@
   <sheets>
     <sheet name="Misiones" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Matriz" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Plan" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Chequeo" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Pools" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Plan" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Misiones'!$A$1:$H$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Matriz'!$A$1:$D$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Plan'!$A$1:$H$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Misiones'!$A$1:$J$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Matriz'!$A$1:$E$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Chequeo'!$A$1:$F$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Pools'!$A$1:$C$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Plan'!$A$1:$J$43</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -42,7 +46,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -56,17 +60,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F4CCCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="002C3E50"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="007F7F7F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000F766E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0092400E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -88,19 +102,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -468,17 +488,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:J43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="55" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -499,113 +521,143 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>tipo_evento</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>paso</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>sección</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>responsables</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>detalle</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>estado</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_mision</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46118</v>
+        <v>46100</v>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46132</v>
+        <v>46107</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Certamen 1</t>
+          <t>Control lógica 2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>pedir_preguntas</t>
+          <t>Control</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Equipo docente</t>
+          <t>construir_control</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Todos</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cada profesor propone preguntas para el certamen. — (inventado)</t>
+          <t>TY</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Construcción del control. — Control lógica 2 — Tema: Lógica 2</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>2026-03-19||2026-03-26||Control lógica 2||Control||construir_control||Sección 1||TY</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46125</v>
+        <v>46107</v>
       </c>
       <c r="B3" s="3" t="n">
-        <v>46132</v>
+        <v>46114</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Certamen 1</t>
+          <t>Control lógica 3</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>construir_control</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Equipo docente</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>p1, p2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Construcción del certamen. — (inventado)</t>
+          <t>MB</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Construcción del control. — Control lógica 3 — Tema: Lógica 3</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2026-03-26||2026-04-02||Control lógica 3||Control||construir_control||Sección 1||MB</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B4" s="3" t="n">
         <v>46127</v>
       </c>
-      <c r="B4" s="3" t="n">
-        <v>46132</v>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>Certamen 1</t>
@@ -613,112 +665,142 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>pauta_prueba</t>
+          <t>Certamen</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Equipo docente</t>
+          <t>pedir_preguntas</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>p4, p3</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pauta del certamen. — (inventado)</t>
+          <t>TY, MB, GM, XX</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Enviar preguntas para certamen con solución. — Certamen 1 — Tema: Certamen 1</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2026-04-01||2026-04-15||Certamen 1||Certamen||pedir_preguntas||Sección 1||TY, MB, GM, XX</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46129</v>
+        <v>46114</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>46132</v>
+        <v>46107</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Certamen 1</t>
+          <t>Control lógica 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>revisar_prueba</t>
+          <t>Control</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Equipo docente</t>
+          <t>corregir_y_notas</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Revisión final del certamen. — (inventado)</t>
+          <t>TY</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Corregir control y subir notas. — Control lógica 2 — Tema: Lógica 2</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-04-02||2026-03-26||Control lógica 2||Control||corregir_y_notas||Sección 1||TY</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46134</v>
+        <v>46114</v>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46132</v>
+        <v>46107</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Certamen 1</t>
+          <t>Control lógica 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>escanear</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Equipo docente</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Escanear certamen y subir a carpeta. — (inventado)</t>
+          <t>TY</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Escanear control y subir a carpeta. — Control lógica 2 — Tema: Lógica 2</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-04-02||2026-03-26||Control lógica 2||Control||escanear||Sección 1||TY</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46146</v>
+        <v>46120</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>46132</v>
+        <v>46127</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -727,222 +809,1770 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>corregir_y_notas</t>
+          <t>Certamen</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Equipo docente</t>
+          <t>construir_control</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Corregir certamen y subir notas. — (inventado)</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Construcción del certamen. — Certamen 1 — Tema: Certamen 1</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-04-08||2026-04-15||Certamen 1||Certamen||construir_control||Sección 1||CC</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46195</v>
+        <v>46121</v>
       </c>
       <c r="B8" s="3" t="n">
-        <v>46181</v>
+        <v>46114</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Trabajo práctico</t>
+          <t>Control lógica 3</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>revisar_tp</t>
+          <t>Control</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Equipo docente</t>
+          <t>corregir_y_notas</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Todos</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Revisar TP y subir nota. — (inventado)</t>
+          <t>MB</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Corregir control y subir notas. — Control lógica 3 — Tema: Lógica 3</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-04-09||2026-04-02||Control lógica 3||Control||corregir_y_notas||Sección 1||MB</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46202</v>
+        <v>46121</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>46223</v>
+        <v>46114</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Examen</t>
+          <t>Control lógica 3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>pedir_preguntas</t>
+          <t>Control</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Equipo docente</t>
+          <t>escanear</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Todos</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Preguntas para examen. — (inventado)</t>
+          <t>MB</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Escanear control y subir a carpeta. — Control lógica 3 — Tema: Lógica 3</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-04-09||2026-04-02||Control lógica 3||Control||escanear||Sección 1||MB</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46209</v>
+        <v>46123</v>
       </c>
       <c r="B10" s="3" t="n">
-        <v>46223</v>
+        <v>46127</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Examen</t>
+          <t>Certamen 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>construir_examen</t>
+          <t>Certamen</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Equipo docente</t>
+          <t>pauta_prueba</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>p4, p3</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Construcción del examen. — (inventado)</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pauta del certamen. — Certamen 1 — Tema: Certamen 1</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-04-11||2026-04-15||Certamen 1||Certamen||pauta_prueba||Sección 1||CC</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46216</v>
+        <v>46134</v>
       </c>
       <c r="B11" s="3" t="n">
-        <v>46223</v>
+        <v>46127</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Examen</t>
+          <t>Certamen 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>pauta_examen</t>
+          <t>Certamen</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Equipo docente</t>
+          <t>corregir_y_notas</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>p2, p1</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pauta del examen. — (inventado)</t>
+          <t>TY, MB, GM, XX</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Corregir certamen y subir notas. — Certamen 1 — Tema: Certamen 1</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-04-22||2026-04-15||Certamen 1||Certamen||corregir_y_notas||Sección 1||TY, MB, GM, XX</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>46237</v>
+        <v>46135</v>
       </c>
       <c r="B12" s="3" t="n">
-        <v>46223</v>
+        <v>46142</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>Control Modelos y Derivadas 2</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>construir_control</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Construcción del control. — Control Modelos y Derivadas 2 — Tema: Modelos y Derivadas 3</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>2026-04-23||2026-04-30||Control Modelos y Derivadas 2||Control||construir_control||Sección 1||GM</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>46149</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Control Modelos y Derivadas 3</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>construir_control</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>XX</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Construcción del control. — Control Modelos y Derivadas 3 — Tema: Modelos y Derivadas 4</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>2026-04-30||2026-05-07||Control Modelos y Derivadas 3||Control||construir_control||Sección 1||XX</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>46142</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Control Modelos y Derivadas 2</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>corregir_y_notas</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Corregir control y subir notas. — Control Modelos y Derivadas 2 — Tema: Modelos y Derivadas 3</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2026-05-07||2026-04-30||Control Modelos y Derivadas 2||Control||corregir_y_notas||Sección 1||GM</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>46142</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Control Modelos y Derivadas 2</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>escanear</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Escanear control y subir a carpeta. — Control Modelos y Derivadas 2 — Tema: Modelos y Derivadas 3</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2026-05-07||2026-04-30||Control Modelos y Derivadas 2||Control||escanear||Sección 1||GM</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>46156</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Control Modelos y Derivadas 4</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>construir_control</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>TY</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Construcción del control. — Control Modelos y Derivadas 4 — Tema: Modelos y Derivadas 5</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2026-05-07||2026-05-14||Control Modelos y Derivadas 4||Control||construir_control||Sección 1||TY</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>46155</v>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>46169</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Certamen 2</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Certamen</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>pedir_preguntas</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>TY, MB, GM, XX</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Enviar preguntas para certamen con solución. — Certamen 2 — Tema: Certamen 2</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2026-05-13||2026-05-27||Certamen 2||Certamen||pedir_preguntas||Sección 1||TY, MB, GM, XX</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>46149</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Control Modelos y Derivadas 3</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>corregir_y_notas</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>XX</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Corregir control y subir notas. — Control Modelos y Derivadas 3 — Tema: Modelos y Derivadas 4</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2026-05-14||2026-05-07||Control Modelos y Derivadas 3||Control||corregir_y_notas||Sección 1||XX</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>46149</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Control Modelos y Derivadas 3</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>escanear</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>XX</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Escanear control y subir a carpeta. — Control Modelos y Derivadas 3 — Tema: Modelos y Derivadas 4</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2026-05-14||2026-05-07||Control Modelos y Derivadas 3||Control||escanear||Sección 1||XX</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>46169</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Certamen 2</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Certamen</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>construir_control</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Construcción del certamen. — Certamen 2 — Tema: Certamen 2</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2026-05-20||2026-05-27||Certamen 2||Certamen||construir_control||Sección 1||CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>46156</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Control Modelos y Derivadas 4</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>corregir_y_notas</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>TY</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Corregir control y subir notas. — Control Modelos y Derivadas 4 — Tema: Modelos y Derivadas 5</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>2026-05-21||2026-05-14||Control Modelos y Derivadas 4||Control||corregir_y_notas||Sección 1||TY</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>46156</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Control Modelos y Derivadas 4</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>escanear</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>TY</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Escanear control y subir a carpeta. — Control Modelos y Derivadas 4 — Tema: Modelos y Derivadas 5</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2026-05-21||2026-05-14||Control Modelos y Derivadas 4||Control||escanear||Sección 1||TY</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>46169</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Certamen 2</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Certamen</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>pauta_prueba</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Pauta del certamen. — Certamen 2 — Tema: Certamen 2</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>2026-05-23||2026-05-27||Certamen 2||Certamen||pauta_prueba||Sección 1||CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>46169</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Certamen 2</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Certamen</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>corregir_y_notas</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>TY, MB, GM, XX</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Corregir certamen y subir notas. — Certamen 2 — Tema: Certamen 2</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>2026-06-03||2026-05-27||Certamen 2||Certamen||corregir_y_notas||Sección 1||TY, MB, GM, XX</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>46177</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Trabajo Práctico</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Trabajo práctico</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>revisar_tp</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>TY, MB, GM, XX</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Revisar TP y subir nota. — Trabajo Práctico — Tema: Linealización de modelos</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>2026-06-11||2026-06-04||Trabajo Práctico||Trabajo práctico||revisar_tp||Sección 1||TY, MB, GM, XX</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>46191</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Control Trigonometría y Vectores 2</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>construir_control</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>MB</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Construcción del control. — Control Trigonometría y Vectores 2 — Tema: Trigonometría y Vectores 2</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>2026-06-11||2026-06-18||Control Trigonometría y Vectores 2||Control||construir_control||Sección 1||MB</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Certamen 3</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Certamen</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>pedir_preguntas</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>TY, MB, GM, XX</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Enviar preguntas para certamen con solución. — Certamen 3 — Tema: Certamen 3</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2026-06-17||2026-07-01||Certamen 3||Certamen||pedir_preguntas||Sección 1||TY, MB, GM, XX</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>46191</v>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>46198</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Control Trigonometría y Vectores 3</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>construir_control</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Construcción del control. — Control Trigonometría y Vectores 3 — Tema: Trigonometría y Vectores 3</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>2026-06-18||2026-06-25||Control Trigonometría y Vectores 3||Control||construir_control||Sección 1||GM</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Certamen 3</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Certamen</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>construir_control</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Construcción del certamen. — Certamen 3 — Tema: Certamen 3</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>2026-06-24||2026-07-01||Certamen 3||Certamen||construir_control||Sección 1||CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>46198</v>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>46191</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Control Trigonometría y Vectores 2</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>corregir_y_notas</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>MB</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Corregir control y subir notas. — Control Trigonometría y Vectores 2 — Tema: Trigonometría y Vectores 2</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>2026-06-25||2026-06-18||Control Trigonometría y Vectores 2||Control||corregir_y_notas||Sección 1||MB</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>46198</v>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>46191</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Control Trigonometría y Vectores 2</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>escanear</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>MB</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Escanear control y subir a carpeta. — Control Trigonometría y Vectores 2 — Tema: Trigonometría y Vectores 2</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>2026-06-25||2026-06-18||Control Trigonometría y Vectores 2||Control||escanear||Sección 1||MB</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>46200</v>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Certamen 3</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Certamen</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>pauta_prueba</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Pauta del certamen. — Certamen 3 — Tema: Certamen 3</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>2026-06-27||2026-07-01||Certamen 3||Certamen||pauta_prueba||Sección 1||CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>46218</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Examen 1</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
           <t>Examen</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>pedir_preguntas</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>TY, MB, GM, XX</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Preguntas para examen con solución. — Examen 1 — Tema: Examen Primera Oportunidad</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>2026-07-01||2026-07-15||Examen 1||Examen||pedir_preguntas||Sección 1||TY, MB, GM, XX</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>46198</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Control Trigonometría y Vectores 3</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>corregir_y_notas</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Corregir control y subir notas. — Control Trigonometría y Vectores 3 — Tema: Trigonometría y Vectores 3</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>2026-07-02||2026-06-25||Control Trigonometría y Vectores 3||Control||corregir_y_notas||Sección 1||GM</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>46198</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Control Trigonometría y Vectores 3</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>escanear</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Escanear control y subir a carpeta. — Control Trigonometría y Vectores 3 — Tema: Trigonometría y Vectores 3</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>2026-07-02||2026-06-25||Control Trigonometría y Vectores 3||Control||escanear||Sección 1||GM</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Certamen 3</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Certamen</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>corregir_y_notas</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>TY, MB, GM, XX</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Corregir certamen y subir notas. — Certamen 3 — Tema: Certamen 3</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>2026-07-08||2026-07-01||Certamen 3||Certamen||corregir_y_notas||Sección 1||TY, MB, GM, XX</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>46218</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Examen 1</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>construir_examen</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Construcción del examen. — Examen 1 — Tema: Examen Primera Oportunidad</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>2026-07-08||2026-07-15||Examen 1||Examen||construir_examen||Sección 1||CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>46225</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Examen 2</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>pedir_preguntas</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>TY, MB, GM, XX</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Preguntas para examen con solución. — Examen 2 — Tema: Examen Segunda Oportunidad</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>2026-07-08||2026-07-22||Examen 2||Examen||pedir_preguntas||Sección 1||TY, MB, GM, XX</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>46214</v>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>46218</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Examen 1</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>pauta_examen</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Pauta del examen. — Examen 1 — Tema: Examen Primera Oportunidad</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>2026-07-11||2026-07-15||Examen 1||Examen||pauta_examen||Sección 1||CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>46225</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Examen 2</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>construir_examen</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Construcción del examen. — Examen 2 — Tema: Examen Segunda Oportunidad</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>2026-07-15||2026-07-22||Examen 2||Examen||construir_examen||Sección 1||CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>46221</v>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>46225</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Examen 2</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>pauta_examen</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Pauta del examen. — Examen 2 — Tema: Examen Segunda Oportunidad</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>2026-07-18||2026-07-22||Examen 2||Examen||pauta_examen||Sección 1||CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>46225</v>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>46218</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Examen 1</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
         <is>
           <t>corregir_examen</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Equipo docente</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>p4</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Corregir examen. — (inventado)</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>TY, MB, GM, XX</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Corregir examen. — Examen 1 — Tema: Examen Primera Oportunidad</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>2026-07-22||2026-07-15||Examen 1||Examen||corregir_examen||Sección 1||TY, MB, GM, XX</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>46225</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Examen 2</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>corregir_examen</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>TY, MB, GM, XX</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Corregir examen. — Examen 2 — Tema: Examen Segunda Oportunidad</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2026-07-29||2026-07-22||Examen 2||Examen||corregir_examen||Sección 1||TY, MB, GM, XX</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H12"/>
+  <autoFilter ref="A1:J43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -953,13 +2583,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -970,17 +2601,22 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
           <t>Misión</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>Detalle</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>Equipo docente</t>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Sección 1 (Miércoles)</t>
         </is>
       </c>
     </row>
@@ -992,17 +2628,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>Certamen</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>construir_control</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Construcción del certamen. — (inventado)</t>
-        </is>
-      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>p1, p2</t>
+          <t>Construcción del certamen. — Certamen 1 — Tema: Certamen 1</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>CC</t>
         </is>
       </c>
     </row>
@@ -1014,17 +2655,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Certamen</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>corregir_y_notas</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Corregir certamen y subir notas. — (inventado)</t>
-        </is>
-      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>Corregir certamen y subir notas. — Certamen 1 — Tema: Certamen 1</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>TY, MB, GM, XX</t>
         </is>
       </c>
     </row>
@@ -1036,17 +2682,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>escanear</t>
+          <t>Certamen</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Escanear certamen y subir a carpeta. — (inventado)</t>
+          <t>pauta_prueba</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>Pauta del certamen. — Certamen 1 — Tema: Certamen 1</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>CC</t>
         </is>
       </c>
     </row>
@@ -1058,176 +2709,1053 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>pauta_prueba</t>
+          <t>Certamen</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Pauta del certamen. — (inventado)</t>
+          <t>pedir_preguntas</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>p4, p3</t>
+          <t>Enviar preguntas para certamen con solución. — Certamen 1 — Tema: Certamen 1</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>TY, MB, GM, XX</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Certamen 1</t>
+          <t>Certamen 2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>pedir_preguntas</t>
+          <t>Certamen</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cada profesor propone preguntas para el certamen. — (inventado)</t>
+          <t>construir_control</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Todos</t>
+          <t>Construcción del certamen. — Certamen 2 — Tema: Certamen 2</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>CC</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Certamen 1</t>
+          <t>Certamen 2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>revisar_prueba</t>
+          <t>Certamen</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Revisión final del certamen. — (inventado)</t>
+          <t>corregir_y_notas</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>Corregir certamen y subir notas. — Certamen 2 — Tema: Certamen 2</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>TY, MB, GM, XX</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Examen</t>
+          <t>Certamen 2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>construir_examen</t>
+          <t>Certamen</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Construcción del examen. — (inventado)</t>
+          <t>pauta_prueba</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>p4, p3</t>
+          <t>Pauta del certamen. — Certamen 2 — Tema: Certamen 2</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>CC</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Examen</t>
+          <t>Certamen 2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>corregir_examen</t>
+          <t>Certamen</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Corregir examen. — (inventado)</t>
+          <t>pedir_preguntas</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>Enviar preguntas para certamen con solución. — Certamen 2 — Tema: Certamen 2</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>TY, MB, GM, XX</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Examen</t>
+          <t>Certamen 3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>pauta_examen</t>
+          <t>Certamen</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pauta del examen. — (inventado)</t>
+          <t>construir_control</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>p2, p1</t>
+          <t>Construcción del certamen. — Certamen 3 — Tema: Certamen 3</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>CC</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Examen</t>
+          <t>Certamen 3</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>pedir_preguntas</t>
+          <t>Certamen</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Preguntas para examen. — (inventado)</t>
+          <t>corregir_y_notas</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Todos</t>
+          <t>Corregir certamen y subir notas. — Certamen 3 — Tema: Certamen 3</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>TY, MB, GM, XX</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Certamen 3</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Certamen</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>pauta_prueba</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Pauta del certamen. — Certamen 3 — Tema: Certamen 3</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Certamen 3</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Certamen</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>pedir_preguntas</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Enviar preguntas para certamen con solución. — Certamen 3 — Tema: Certamen 3</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>TY, MB, GM, XX</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Control Modelos y Derivadas 2</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>construir_control</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Construcción del control. — Control Modelos y Derivadas 2 — Tema: Modelos y Derivadas 3</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Control Modelos y Derivadas 2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>corregir_y_notas</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Corregir control y subir notas. — Control Modelos y Derivadas 2 — Tema: Modelos y Derivadas 3</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Control Modelos y Derivadas 2</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>escanear</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Escanear control y subir a carpeta. — Control Modelos y Derivadas 2 — Tema: Modelos y Derivadas 3</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Control Modelos y Derivadas 3</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>construir_control</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Construcción del control. — Control Modelos y Derivadas 3 — Tema: Modelos y Derivadas 4</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>XX</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Control Modelos y Derivadas 3</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>corregir_y_notas</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Corregir control y subir notas. — Control Modelos y Derivadas 3 — Tema: Modelos y Derivadas 4</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>XX</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Control Modelos y Derivadas 3</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>escanear</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Escanear control y subir a carpeta. — Control Modelos y Derivadas 3 — Tema: Modelos y Derivadas 4</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>XX</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Control Modelos y Derivadas 4</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>construir_control</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Construcción del control. — Control Modelos y Derivadas 4 — Tema: Modelos y Derivadas 5</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>TY</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Control Modelos y Derivadas 4</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>corregir_y_notas</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Corregir control y subir notas. — Control Modelos y Derivadas 4 — Tema: Modelos y Derivadas 5</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>TY</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Control Modelos y Derivadas 4</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>escanear</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Escanear control y subir a carpeta. — Control Modelos y Derivadas 4 — Tema: Modelos y Derivadas 5</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>TY</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Control Trigonometría y Vectores 2</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>construir_control</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Construcción del control. — Control Trigonometría y Vectores 2 — Tema: Trigonometría y Vectores 2</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>MB</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Control Trigonometría y Vectores 2</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>corregir_y_notas</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Corregir control y subir notas. — Control Trigonometría y Vectores 2 — Tema: Trigonometría y Vectores 2</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>MB</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Control Trigonometría y Vectores 2</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>escanear</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Escanear control y subir a carpeta. — Control Trigonometría y Vectores 2 — Tema: Trigonometría y Vectores 2</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>MB</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Control Trigonometría y Vectores 3</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>construir_control</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Construcción del control. — Control Trigonometría y Vectores 3 — Tema: Trigonometría y Vectores 3</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Control Trigonometría y Vectores 3</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>corregir_y_notas</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Corregir control y subir notas. — Control Trigonometría y Vectores 3 — Tema: Trigonometría y Vectores 3</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Control Trigonometría y Vectores 3</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>escanear</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Escanear control y subir a carpeta. — Control Trigonometría y Vectores 3 — Tema: Trigonometría y Vectores 3</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Control lógica 2</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>construir_control</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Construcción del control. — Control lógica 2 — Tema: Lógica 2</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>TY</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Control lógica 2</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>corregir_y_notas</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Corregir control y subir notas. — Control lógica 2 — Tema: Lógica 2</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>TY</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Control lógica 2</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>escanear</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Escanear control y subir a carpeta. — Control lógica 2 — Tema: Lógica 2</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>TY</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Control lógica 3</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>construir_control</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Construcción del control. — Control lógica 3 — Tema: Lógica 3</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>MB</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Control lógica 3</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>corregir_y_notas</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Corregir control y subir notas. — Control lógica 3 — Tema: Lógica 3</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>MB</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Control lógica 3</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>escanear</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Escanear control y subir a carpeta. — Control lógica 3 — Tema: Lógica 3</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>MB</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Examen 1</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>construir_examen</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Construcción del examen. — Examen 1 — Tema: Examen Primera Oportunidad</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Examen 1</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>corregir_examen</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Corregir examen. — Examen 1 — Tema: Examen Primera Oportunidad</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>TY, MB, GM, XX</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Examen 1</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>pauta_examen</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Pauta del examen. — Examen 1 — Tema: Examen Primera Oportunidad</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Examen 1</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>pedir_preguntas</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Preguntas para examen con solución. — Examen 1 — Tema: Examen Primera Oportunidad</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>TY, MB, GM, XX</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Examen 2</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>construir_examen</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Construcción del examen. — Examen 2 — Tema: Examen Segunda Oportunidad</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Examen 2</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>corregir_examen</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Corregir examen. — Examen 2 — Tema: Examen Segunda Oportunidad</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>TY, MB, GM, XX</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Examen 2</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>pauta_examen</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Pauta del examen. — Examen 2 — Tema: Examen Segunda Oportunidad</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Examen 2</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>pedir_preguntas</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Preguntas para examen con solución. — Examen 2 — Tema: Examen Segunda Oportunidad</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>TY, MB, GM, XX</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Trabajo Práctico</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
           <t>Trabajo práctico</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>revisar_tp</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Revisar TP y subir nota. — (inventado)</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Todos</t>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Revisar TP y subir nota. — Trabajo Práctico — Tema: Linealización de modelos</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>TY, MB, GM, XX</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D12"/>
+  <autoFilter ref="A1:E43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1238,481 +3766,2461 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>sección</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>fecha_evento</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>evento</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>observaciones</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>slot_pool</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>responsable_control</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>46107</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Control lógica 2</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Control lógica 2</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>TY</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>46114</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Control lógica 3</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Control lógica 3</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>MB</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>46142</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Control Modelos y Derivadas 2</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Control Modelos y Derivadas 2</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>46149</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Control Modelos y Derivadas 3</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Control Modelos y Derivadas 3</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>XX</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>46156</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Control Modelos y Derivadas 4</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Control Modelos y Derivadas 4</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>TY</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>46191</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Control Trigonometría y Vectores 2</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Control Trigonometría y Vectores 2</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>MB</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>46198</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Control Trigonometría y Vectores 3</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Control Trigonometría y Vectores 3</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F8"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>sección</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>slot</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>profesor</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>TY</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>MB</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>XX</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="55" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>fecha_limite</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>fecha_evento</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>evento</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>tipo_evento</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>paso</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>sección</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="G1" s="7" t="inlineStr">
         <is>
           <t>responsables</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="H1" s="7" t="inlineStr">
         <is>
           <t>detalle</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="I1" s="7" t="inlineStr">
         <is>
           <t>estado</t>
+        </is>
+      </c>
+      <c r="J1" s="7" t="inlineStr">
+        <is>
+          <t>id_mision</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>46118</v>
+        <v>46100</v>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46132</v>
+        <v>46107</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Certamen 1</t>
+          <t>Control lógica 2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>pedir_preguntas</t>
+          <t>Control</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Equipo docente</t>
+          <t>construir_control</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Todos</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cada profesor propone preguntas para el certamen. — (inventado)</t>
+          <t>TY</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Construcción del control. — Control lógica 2 — Tema: Lógica 2</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>2026-03-19||2026-03-26||Control lógica 2||Control||construir_control||Sección 1||TY</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>46125</v>
+        <v>46114</v>
       </c>
       <c r="B3" s="3" t="n">
-        <v>46132</v>
+        <v>46107</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Certamen 1</t>
+          <t>Control lógica 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>construir_control</t>
+          <t>Control</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Equipo docente</t>
+          <t>escanear</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>p1, p2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Construcción del certamen. — (inventado)</t>
+          <t>TY</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Escanear control y subir a carpeta. — Control lógica 2 — Tema: Lógica 2</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2026-04-02||2026-03-26||Control lógica 2||Control||escanear||Sección 1||TY</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>46127</v>
+        <v>46114</v>
       </c>
       <c r="B4" s="3" t="n">
-        <v>46132</v>
+        <v>46107</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Certamen 1</t>
+          <t>Control lógica 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>pauta_prueba</t>
+          <t>Control</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Equipo docente</t>
+          <t>corregir_y_notas</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>p4, p3</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pauta del certamen. — (inventado)</t>
+          <t>TY</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Corregir control y subir notas. — Control lógica 2 — Tema: Lógica 2</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2026-04-02||2026-03-26||Control lógica 2||Control||corregir_y_notas||Sección 1||TY</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>46129</v>
+        <v>46107</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>46132</v>
+        <v>46114</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Certamen 1</t>
+          <t>Control lógica 3</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>revisar_prueba</t>
+          <t>Control</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Equipo docente</t>
+          <t>construir_control</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Revisión final del certamen. — (inventado)</t>
+          <t>MB</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Construcción del control. — Control lógica 3 — Tema: Lógica 3</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-03-26||2026-04-02||Control lógica 3||Control||construir_control||Sección 1||MB</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>46134</v>
+        <v>46121</v>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46132</v>
+        <v>46114</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Certamen 1</t>
+          <t>Control lógica 3</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>escanear</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Equipo docente</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Escanear certamen y subir a carpeta. — (inventado)</t>
+          <t>MB</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Escanear control y subir a carpeta. — Control lógica 3 — Tema: Lógica 3</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-04-09||2026-04-02||Control lógica 3||Control||escanear||Sección 1||MB</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>46146</v>
+        <v>46121</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>46132</v>
+        <v>46114</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Certamen 1</t>
+          <t>Control lógica 3</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>corregir_y_notas</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Equipo docente</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Corregir certamen y subir notas. — (inventado)</t>
+          <t>MB</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Corregir control y subir notas. — Control lógica 3 — Tema: Lógica 3</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-04-09||2026-04-02||Control lógica 3||Control||corregir_y_notas||Sección 1||MB</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>46202</v>
+        <v>46113</v>
       </c>
       <c r="B8" s="3" t="n">
-        <v>46223</v>
+        <v>46127</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Examen</t>
+          <t>Certamen 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>Certamen</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>pedir_preguntas</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Equipo docente</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Todos</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Preguntas para examen. — (inventado)</t>
+          <t>TY, MB, GM, XX</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Enviar preguntas para certamen con solución. — Certamen 1 — Tema: Certamen 1</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-04-01||2026-04-15||Certamen 1||Certamen||pedir_preguntas||Sección 1||TY, MB, GM, XX</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>46209</v>
+        <v>46120</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>46223</v>
+        <v>46127</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Examen</t>
+          <t>Certamen 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>construir_examen</t>
+          <t>Certamen</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Equipo docente</t>
+          <t>construir_control</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>p4, p3</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Construcción del examen. — (inventado)</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Construcción del certamen. — Certamen 1 — Tema: Certamen 1</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-04-08||2026-04-15||Certamen 1||Certamen||construir_control||Sección 1||CC</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>46216</v>
+        <v>46123</v>
       </c>
       <c r="B10" s="3" t="n">
-        <v>46223</v>
+        <v>46127</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Examen</t>
+          <t>Certamen 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>pauta_examen</t>
+          <t>Certamen</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Equipo docente</t>
+          <t>pauta_prueba</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>p2, p1</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pauta del examen. — (inventado)</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pauta del certamen. — Certamen 1 — Tema: Certamen 1</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-04-11||2026-04-15||Certamen 1||Certamen||pauta_prueba||Sección 1||CC</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>46237</v>
+        <v>46134</v>
       </c>
       <c r="B11" s="3" t="n">
-        <v>46223</v>
+        <v>46127</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Examen</t>
+          <t>Certamen 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>corregir_examen</t>
+          <t>Certamen</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Equipo docente</t>
+          <t>corregir_y_notas</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Corregir examen. — (inventado)</t>
+          <t>TY, MB, GM, XX</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Corregir certamen y subir notas. — Certamen 1 — Tema: Certamen 1</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-04-22||2026-04-15||Certamen 1||Certamen||corregir_y_notas||Sección 1||TY, MB, GM, XX</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>46195</v>
+        <v>46135</v>
       </c>
       <c r="B12" s="3" t="n">
-        <v>46181</v>
+        <v>46142</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>Control Modelos y Derivadas 2</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>construir_control</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Construcción del control. — Control Modelos y Derivadas 2 — Tema: Modelos y Derivadas 3</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>2026-04-23||2026-04-30||Control Modelos y Derivadas 2||Control||construir_control||Sección 1||GM</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>46142</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Control Modelos y Derivadas 2</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>escanear</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Escanear control y subir a carpeta. — Control Modelos y Derivadas 2 — Tema: Modelos y Derivadas 3</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>2026-05-07||2026-04-30||Control Modelos y Derivadas 2||Control||escanear||Sección 1||GM</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>46142</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Control Modelos y Derivadas 2</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>corregir_y_notas</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Corregir control y subir notas. — Control Modelos y Derivadas 2 — Tema: Modelos y Derivadas 3</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2026-05-07||2026-04-30||Control Modelos y Derivadas 2||Control||corregir_y_notas||Sección 1||GM</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>46149</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Control Modelos y Derivadas 3</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>construir_control</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>XX</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Construcción del control. — Control Modelos y Derivadas 3 — Tema: Modelos y Derivadas 4</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2026-04-30||2026-05-07||Control Modelos y Derivadas 3||Control||construir_control||Sección 1||XX</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>46149</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Control Modelos y Derivadas 3</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>escanear</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>XX</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Escanear control y subir a carpeta. — Control Modelos y Derivadas 3 — Tema: Modelos y Derivadas 4</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2026-05-14||2026-05-07||Control Modelos y Derivadas 3||Control||escanear||Sección 1||XX</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>46149</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Control Modelos y Derivadas 3</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>corregir_y_notas</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>XX</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Corregir control y subir notas. — Control Modelos y Derivadas 3 — Tema: Modelos y Derivadas 4</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2026-05-14||2026-05-07||Control Modelos y Derivadas 3||Control||corregir_y_notas||Sección 1||XX</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>46156</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Control Modelos y Derivadas 4</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>construir_control</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>TY</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Construcción del control. — Control Modelos y Derivadas 4 — Tema: Modelos y Derivadas 5</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2026-05-07||2026-05-14||Control Modelos y Derivadas 4||Control||construir_control||Sección 1||TY</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>46156</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Control Modelos y Derivadas 4</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>escanear</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>TY</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Escanear control y subir a carpeta. — Control Modelos y Derivadas 4 — Tema: Modelos y Derivadas 5</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2026-05-21||2026-05-14||Control Modelos y Derivadas 4||Control||escanear||Sección 1||TY</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>46156</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Control Modelos y Derivadas 4</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>corregir_y_notas</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>TY</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Corregir control y subir notas. — Control Modelos y Derivadas 4 — Tema: Modelos y Derivadas 5</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2026-05-21||2026-05-14||Control Modelos y Derivadas 4||Control||corregir_y_notas||Sección 1||TY</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>46155</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>46169</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Certamen 2</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Certamen</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>pedir_preguntas</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>TY, MB, GM, XX</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Enviar preguntas para certamen con solución. — Certamen 2 — Tema: Certamen 2</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>2026-05-13||2026-05-27||Certamen 2||Certamen||pedir_preguntas||Sección 1||TY, MB, GM, XX</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>46169</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Certamen 2</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Certamen</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>construir_control</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Construcción del certamen. — Certamen 2 — Tema: Certamen 2</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2026-05-20||2026-05-27||Certamen 2||Certamen||construir_control||Sección 1||CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>46169</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Certamen 2</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Certamen</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>pauta_prueba</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Pauta del certamen. — Certamen 2 — Tema: Certamen 2</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>2026-05-23||2026-05-27||Certamen 2||Certamen||pauta_prueba||Sección 1||CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>46169</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Certamen 2</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Certamen</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>corregir_y_notas</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>TY, MB, GM, XX</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Corregir certamen y subir notas. — Certamen 2 — Tema: Certamen 2</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>2026-06-03||2026-05-27||Certamen 2||Certamen||corregir_y_notas||Sección 1||TY, MB, GM, XX</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>46177</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Trabajo Práctico</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
           <t>Trabajo práctico</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>revisar_tp</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Equipo docente</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Todos</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Revisar TP y subir nota. — (inventado)</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>TY, MB, GM, XX</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Revisar TP y subir nota. — Trabajo Práctico — Tema: Linealización de modelos</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>2026-06-11||2026-06-04||Trabajo Práctico||Trabajo práctico||revisar_tp||Sección 1||TY, MB, GM, XX</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>46191</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Control Trigonometría y Vectores 2</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>construir_control</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>MB</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Construcción del control. — Control Trigonometría y Vectores 2 — Tema: Trigonometría y Vectores 2</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>2026-06-11||2026-06-18||Control Trigonometría y Vectores 2||Control||construir_control||Sección 1||MB</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>46198</v>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>46191</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Control Trigonometría y Vectores 2</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>escanear</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>MB</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Escanear control y subir a carpeta. — Control Trigonometría y Vectores 2 — Tema: Trigonometría y Vectores 2</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2026-06-25||2026-06-18||Control Trigonometría y Vectores 2||Control||escanear||Sección 1||MB</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="n">
+        <v>46198</v>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>46191</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Control Trigonometría y Vectores 2</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>corregir_y_notas</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>MB</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Corregir control y subir notas. — Control Trigonometría y Vectores 2 — Tema: Trigonometría y Vectores 2</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>2026-06-25||2026-06-18||Control Trigonometría y Vectores 2||Control||corregir_y_notas||Sección 1||MB</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>46191</v>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>46198</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Control Trigonometría y Vectores 3</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>construir_control</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Construcción del control. — Control Trigonometría y Vectores 3 — Tema: Trigonometría y Vectores 3</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>2026-06-18||2026-06-25||Control Trigonometría y Vectores 3||Control||construir_control||Sección 1||GM</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>46198</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Control Trigonometría y Vectores 3</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>escanear</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Escanear control y subir a carpeta. — Control Trigonometría y Vectores 3 — Tema: Trigonometría y Vectores 3</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>2026-07-02||2026-06-25||Control Trigonometría y Vectores 3||Control||escanear||Sección 1||GM</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>46198</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Control Trigonometría y Vectores 3</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>corregir_y_notas</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Corregir control y subir notas. — Control Trigonometría y Vectores 3 — Tema: Trigonometría y Vectores 3</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>2026-07-02||2026-06-25||Control Trigonometría y Vectores 3||Control||corregir_y_notas||Sección 1||GM</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Certamen 3</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Certamen</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>pedir_preguntas</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>TY, MB, GM, XX</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Enviar preguntas para certamen con solución. — Certamen 3 — Tema: Certamen 3</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>2026-06-17||2026-07-01||Certamen 3||Certamen||pedir_preguntas||Sección 1||TY, MB, GM, XX</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Certamen 3</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Certamen</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>construir_control</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Construcción del certamen. — Certamen 3 — Tema: Certamen 3</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>2026-06-24||2026-07-01||Certamen 3||Certamen||construir_control||Sección 1||CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="n">
+        <v>46200</v>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Certamen 3</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Certamen</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>pauta_prueba</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Pauta del certamen. — Certamen 3 — Tema: Certamen 3</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>2026-06-27||2026-07-01||Certamen 3||Certamen||pauta_prueba||Sección 1||CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Certamen 3</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Certamen</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>corregir_y_notas</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>TY, MB, GM, XX</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Corregir certamen y subir notas. — Certamen 3 — Tema: Certamen 3</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>2026-07-08||2026-07-01||Certamen 3||Certamen||corregir_y_notas||Sección 1||TY, MB, GM, XX</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>46218</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Examen 1</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>pedir_preguntas</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>TY, MB, GM, XX</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Preguntas para examen con solución. — Examen 1 — Tema: Examen Primera Oportunidad</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>2026-07-01||2026-07-15||Examen 1||Examen||pedir_preguntas||Sección 1||TY, MB, GM, XX</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>46218</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Examen 1</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>construir_examen</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Construcción del examen. — Examen 1 — Tema: Examen Primera Oportunidad</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>2026-07-08||2026-07-15||Examen 1||Examen||construir_examen||Sección 1||CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="n">
+        <v>46214</v>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>46218</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Examen 1</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>pauta_examen</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Pauta del examen. — Examen 1 — Tema: Examen Primera Oportunidad</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>2026-07-11||2026-07-15||Examen 1||Examen||pauta_examen||Sección 1||CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="n">
+        <v>46225</v>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>46218</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Examen 1</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>corregir_examen</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>TY, MB, GM, XX</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Corregir examen. — Examen 1 — Tema: Examen Primera Oportunidad</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>2026-07-22||2026-07-15||Examen 1||Examen||corregir_examen||Sección 1||TY, MB, GM, XX</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>46225</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Examen 2</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>pedir_preguntas</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>TY, MB, GM, XX</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Preguntas para examen con solución. — Examen 2 — Tema: Examen Segunda Oportunidad</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>2026-07-08||2026-07-22||Examen 2||Examen||pedir_preguntas||Sección 1||TY, MB, GM, XX</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>46225</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Examen 2</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>construir_examen</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Construcción del examen. — Examen 2 — Tema: Examen Segunda Oportunidad</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>2026-07-15||2026-07-22||Examen 2||Examen||construir_examen||Sección 1||CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="n">
+        <v>46221</v>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>46225</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Examen 2</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>pauta_examen</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Pauta del examen. — Examen 2 — Tema: Examen Segunda Oportunidad</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>2026-07-18||2026-07-22||Examen 2||Examen||pauta_examen||Sección 1||CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>46225</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Examen 2</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>corregir_examen</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>TY, MB, GM, XX</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Corregir examen. — Examen 2 — Tema: Examen Segunda Oportunidad</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2026-07-29||2026-07-22||Examen 2||Examen||corregir_examen||Sección 1||TY, MB, GM, XX</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H12"/>
+  <autoFilter ref="A1:J43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/tecnologia_medica/misiones.xlsx
+++ b/data/tecnologia_medica/misiones.xlsx
@@ -680,7 +680,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>TY, MB, GM, XX</t>
+          <t>TY, MB, GM, GF</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-04-01||2026-04-15||Certamen 1||Certamen||pedir_preguntas||Sección 1||TY, MB, GM, XX</t>
+          <t>2026-04-01||2026-04-15||Certamen 1||Certamen||pedir_preguntas||Sección 1||TY, MB, GM, GF</t>
         </is>
       </c>
     </row>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>TY, MB, GM, XX</t>
+          <t>TY, MB, GM, GF</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-04-22||2026-04-15||Certamen 1||Certamen||corregir_y_notas||Sección 1||TY, MB, GM, XX</t>
+          <t>2026-04-22||2026-04-15||Certamen 1||Certamen||corregir_y_notas||Sección 1||TY, MB, GM, GF</t>
         </is>
       </c>
     </row>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>XX</t>
+          <t>GF</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-04-30||2026-05-07||Control Modelos y Derivadas 3||Control||construir_control||Sección 1||XX</t>
+          <t>2026-04-30||2026-05-07||Control Modelos y Derivadas 3||Control||construir_control||Sección 1||GF</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>TY, MB, GM, XX</t>
+          <t>TY, MB, GM, GF</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-05-13||2026-05-27||Certamen 2||Certamen||pedir_preguntas||Sección 1||TY, MB, GM, XX</t>
+          <t>2026-05-13||2026-05-27||Certamen 2||Certamen||pedir_preguntas||Sección 1||TY, MB, GM, GF</t>
         </is>
       </c>
     </row>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>XX</t>
+          <t>GF</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-05-14||2026-05-07||Control Modelos y Derivadas 3||Control||corregir_y_notas||Sección 1||XX</t>
+          <t>2026-05-14||2026-05-07||Control Modelos y Derivadas 3||Control||corregir_y_notas||Sección 1||GF</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>XX</t>
+          <t>GF</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1415,7 +1415,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-05-14||2026-05-07||Control Modelos y Derivadas 3||Control||escanear||Sección 1||XX</t>
+          <t>2026-05-14||2026-05-07||Control Modelos y Derivadas 3||Control||escanear||Sección 1||GF</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>TY, MB, GM, XX</t>
+          <t>TY, MB, GM, GF</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-06-03||2026-05-27||Certamen 2||Certamen||corregir_y_notas||Sección 1||TY, MB, GM, XX</t>
+          <t>2026-06-03||2026-05-27||Certamen 2||Certamen||corregir_y_notas||Sección 1||TY, MB, GM, GF</t>
         </is>
       </c>
     </row>
@@ -1688,7 +1688,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>TY, MB, GM, XX</t>
+          <t>TY, MB, GM, GF</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-06-11||2026-06-04||Trabajo Práctico||Trabajo práctico||revisar_tp||Sección 1||TY, MB, GM, XX</t>
+          <t>2026-06-11||2026-06-04||Trabajo Práctico||Trabajo práctico||revisar_tp||Sección 1||TY, MB, GM, GF</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>TY, MB, GM, XX</t>
+          <t>TY, MB, GM, GF</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-06-17||2026-07-01||Certamen 3||Certamen||pedir_preguntas||Sección 1||TY, MB, GM, XX</t>
+          <t>2026-06-17||2026-07-01||Certamen 3||Certamen||pedir_preguntas||Sección 1||TY, MB, GM, GF</t>
         </is>
       </c>
     </row>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>TY, MB, GM, XX</t>
+          <t>TY, MB, GM, GF</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2087,7 +2087,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-07-01||2026-07-15||Examen 1||Examen||pedir_preguntas||Sección 1||TY, MB, GM, XX</t>
+          <t>2026-07-01||2026-07-15||Examen 1||Examen||pedir_preguntas||Sección 1||TY, MB, GM, GF</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>TY, MB, GM, XX</t>
+          <t>TY, MB, GM, GF</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-07-08||2026-07-01||Certamen 3||Certamen||corregir_y_notas||Sección 1||TY, MB, GM, XX</t>
+          <t>2026-07-08||2026-07-01||Certamen 3||Certamen||corregir_y_notas||Sección 1||TY, MB, GM, GF</t>
         </is>
       </c>
     </row>
@@ -2312,7 +2312,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>TY, MB, GM, XX</t>
+          <t>TY, MB, GM, GF</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-07-08||2026-07-22||Examen 2||Examen||pedir_preguntas||Sección 1||TY, MB, GM, XX</t>
+          <t>2026-07-08||2026-07-22||Examen 2||Examen||pedir_preguntas||Sección 1||TY, MB, GM, GF</t>
         </is>
       </c>
     </row>
@@ -2504,7 +2504,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>TY, MB, GM, XX</t>
+          <t>TY, MB, GM, GF</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-07-22||2026-07-15||Examen 1||Examen||corregir_examen||Sección 1||TY, MB, GM, XX</t>
+          <t>2026-07-22||2026-07-15||Examen 1||Examen||corregir_examen||Sección 1||TY, MB, GM, GF</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2552,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>TY, MB, GM, XX</t>
+          <t>TY, MB, GM, GF</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2567,7 +2567,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-07-29||2026-07-22||Examen 2||Examen||corregir_examen||Sección 1||TY, MB, GM, XX</t>
+          <t>2026-07-29||2026-07-22||Examen 2||Examen||corregir_examen||Sección 1||TY, MB, GM, GF</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>TY, MB, GM, XX</t>
+          <t>TY, MB, GM, GF</t>
         </is>
       </c>
     </row>
@@ -2724,7 +2724,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>TY, MB, GM, XX</t>
+          <t>TY, MB, GM, GF</t>
         </is>
       </c>
     </row>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>TY, MB, GM, XX</t>
+          <t>TY, MB, GM, GF</t>
         </is>
       </c>
     </row>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>TY, MB, GM, XX</t>
+          <t>TY, MB, GM, GF</t>
         </is>
       </c>
     </row>
@@ -2886,7 +2886,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>TY, MB, GM, XX</t>
+          <t>TY, MB, GM, GF</t>
         </is>
       </c>
     </row>
@@ -2940,7 +2940,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>TY, MB, GM, XX</t>
+          <t>TY, MB, GM, GF</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>XX</t>
+          <t>GF</t>
         </is>
       </c>
     </row>
@@ -3075,7 +3075,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>XX</t>
+          <t>GF</t>
         </is>
       </c>
     </row>
@@ -3102,7 +3102,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>XX</t>
+          <t>GF</t>
         </is>
       </c>
     </row>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>TY, MB, GM, XX</t>
+          <t>TY, MB, GM, GF</t>
         </is>
       </c>
     </row>
@@ -3615,7 +3615,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>TY, MB, GM, XX</t>
+          <t>TY, MB, GM, GF</t>
         </is>
       </c>
     </row>
@@ -3669,7 +3669,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>TY, MB, GM, XX</t>
+          <t>TY, MB, GM, GF</t>
         </is>
       </c>
     </row>
@@ -3723,7 +3723,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>TY, MB, GM, XX</t>
+          <t>TY, MB, GM, GF</t>
         </is>
       </c>
     </row>
@@ -3750,7 +3750,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>TY, MB, GM, XX</t>
+          <t>TY, MB, GM, GF</t>
         </is>
       </c>
     </row>
@@ -3925,7 +3925,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>XX</t>
+          <t>GF</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>XX</t>
+          <t>GF</t>
         </is>
       </c>
     </row>
@@ -4520,7 +4520,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>TY, MB, GM, XX</t>
+          <t>TY, MB, GM, GF</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -4535,7 +4535,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-04-01||2026-04-15||Certamen 1||Certamen||pedir_preguntas||Sección 1||TY, MB, GM, XX</t>
+          <t>2026-04-01||2026-04-15||Certamen 1||Certamen||pedir_preguntas||Sección 1||TY, MB, GM, GF</t>
         </is>
       </c>
     </row>
@@ -4664,7 +4664,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>TY, MB, GM, XX</t>
+          <t>TY, MB, GM, GF</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-04-22||2026-04-15||Certamen 1||Certamen||corregir_y_notas||Sección 1||TY, MB, GM, XX</t>
+          <t>2026-04-22||2026-04-15||Certamen 1||Certamen||corregir_y_notas||Sección 1||TY, MB, GM, GF</t>
         </is>
       </c>
     </row>
@@ -4856,7 +4856,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>XX</t>
+          <t>GF</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-04-30||2026-05-07||Control Modelos y Derivadas 3||Control||construir_control||Sección 1||XX</t>
+          <t>2026-04-30||2026-05-07||Control Modelos y Derivadas 3||Control||construir_control||Sección 1||GF</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>XX</t>
+          <t>GF</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -4919,7 +4919,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-05-14||2026-05-07||Control Modelos y Derivadas 3||Control||escanear||Sección 1||XX</t>
+          <t>2026-05-14||2026-05-07||Control Modelos y Derivadas 3||Control||escanear||Sección 1||GF</t>
         </is>
       </c>
     </row>
@@ -4952,7 +4952,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>XX</t>
+          <t>GF</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-05-14||2026-05-07||Control Modelos y Derivadas 3||Control||corregir_y_notas||Sección 1||XX</t>
+          <t>2026-05-14||2026-05-07||Control Modelos y Derivadas 3||Control||corregir_y_notas||Sección 1||GF</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>TY, MB, GM, XX</t>
+          <t>TY, MB, GM, GF</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -5159,7 +5159,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-05-13||2026-05-27||Certamen 2||Certamen||pedir_preguntas||Sección 1||TY, MB, GM, XX</t>
+          <t>2026-05-13||2026-05-27||Certamen 2||Certamen||pedir_preguntas||Sección 1||TY, MB, GM, GF</t>
         </is>
       </c>
     </row>
@@ -5288,7 +5288,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>TY, MB, GM, XX</t>
+          <t>TY, MB, GM, GF</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-06-03||2026-05-27||Certamen 2||Certamen||corregir_y_notas||Sección 1||TY, MB, GM, XX</t>
+          <t>2026-06-03||2026-05-27||Certamen 2||Certamen||corregir_y_notas||Sección 1||TY, MB, GM, GF</t>
         </is>
       </c>
     </row>
@@ -5336,7 +5336,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>TY, MB, GM, XX</t>
+          <t>TY, MB, GM, GF</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-06-11||2026-06-04||Trabajo Práctico||Trabajo práctico||revisar_tp||Sección 1||TY, MB, GM, XX</t>
+          <t>2026-06-11||2026-06-04||Trabajo Práctico||Trabajo práctico||revisar_tp||Sección 1||TY, MB, GM, GF</t>
         </is>
       </c>
     </row>
@@ -5672,7 +5672,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>TY, MB, GM, XX</t>
+          <t>TY, MB, GM, GF</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -5687,7 +5687,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-06-17||2026-07-01||Certamen 3||Certamen||pedir_preguntas||Sección 1||TY, MB, GM, XX</t>
+          <t>2026-06-17||2026-07-01||Certamen 3||Certamen||pedir_preguntas||Sección 1||TY, MB, GM, GF</t>
         </is>
       </c>
     </row>
@@ -5816,7 +5816,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>TY, MB, GM, XX</t>
+          <t>TY, MB, GM, GF</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-07-08||2026-07-01||Certamen 3||Certamen||corregir_y_notas||Sección 1||TY, MB, GM, XX</t>
+          <t>2026-07-08||2026-07-01||Certamen 3||Certamen||corregir_y_notas||Sección 1||TY, MB, GM, GF</t>
         </is>
       </c>
     </row>
@@ -5864,7 +5864,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>TY, MB, GM, XX</t>
+          <t>TY, MB, GM, GF</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -5879,7 +5879,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-07-01||2026-07-15||Examen 1||Examen||pedir_preguntas||Sección 1||TY, MB, GM, XX</t>
+          <t>2026-07-01||2026-07-15||Examen 1||Examen||pedir_preguntas||Sección 1||TY, MB, GM, GF</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>TY, MB, GM, XX</t>
+          <t>TY, MB, GM, GF</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-07-22||2026-07-15||Examen 1||Examen||corregir_examen||Sección 1||TY, MB, GM, XX</t>
+          <t>2026-07-22||2026-07-15||Examen 1||Examen||corregir_examen||Sección 1||TY, MB, GM, GF</t>
         </is>
       </c>
     </row>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>TY, MB, GM, XX</t>
+          <t>TY, MB, GM, GF</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -6071,7 +6071,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-07-08||2026-07-22||Examen 2||Examen||pedir_preguntas||Sección 1||TY, MB, GM, XX</t>
+          <t>2026-07-08||2026-07-22||Examen 2||Examen||pedir_preguntas||Sección 1||TY, MB, GM, GF</t>
         </is>
       </c>
     </row>
@@ -6200,7 +6200,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>TY, MB, GM, XX</t>
+          <t>TY, MB, GM, GF</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-07-29||2026-07-22||Examen 2||Examen||corregir_examen||Sección 1||TY, MB, GM, XX</t>
+          <t>2026-07-29||2026-07-22||Examen 2||Examen||corregir_examen||Sección 1||TY, MB, GM, GF</t>
         </is>
       </c>
     </row>

--- a/data/tecnologia_medica/misiones.xlsx
+++ b/data/tecnologia_medica/misiones.xlsx
@@ -3830,7 +3830,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>BALANCEADO</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>BALANCEADO</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -3890,7 +3890,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>BALANCEADO</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>BALANCEADO</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>BALANCEADO</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>BALANCEADO</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -4010,7 +4010,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>BALANCEADO</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
